--- a/salidas/Base_productos_PPDJ_python.xlsx
+++ b/salidas/Base_productos_PPDJ_python.xlsx
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="P3" t="n">
         <v>11655</v>
@@ -944,7 +944,7 @@
         <v>157063</v>
       </c>
       <c r="AS3" t="n">
-        <v>25625</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="4">
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5255</v>
       </c>
       <c r="P5" t="n">
         <v>589</v>
@@ -1246,7 +1246,7 @@
         <v>22295</v>
       </c>
       <c r="AS5" t="n">
-        <v>43841</v>
+        <v>52256</v>
       </c>
     </row>
     <row r="6">
@@ -1381,7 +1381,7 @@
         <v>31017</v>
       </c>
       <c r="AS6" t="n">
-        <v>6275</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="7">
@@ -1643,7 +1643,7 @@
         <v>6686</v>
       </c>
       <c r="AS8" t="n">
-        <v>4800</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="9">
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
         <v>55</v>
@@ -1798,7 +1798,7 @@
         <v>3375</v>
       </c>
       <c r="AS9" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -1939,7 +1939,7 @@
         <v>164</v>
       </c>
       <c r="AS10" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P11" t="n">
         <v>8</v>
@@ -2090,7 +2090,7 @@
         <v>133</v>
       </c>
       <c r="AS11" t="n">
-        <v>151</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
@@ -2155,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="P12" t="n">
         <v>59034</v>
@@ -2241,7 +2241,7 @@
         <v>64977</v>
       </c>
       <c r="AS12" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="13">
@@ -2503,7 +2503,7 @@
         <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -2644,7 +2644,7 @@
         <v>41</v>
       </c>
       <c r="AS15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2855,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U17" t="n">
         <v>200</v>
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P18" t="n">
         <v>25</v>
@@ -3077,7 +3077,7 @@
         <v>266</v>
       </c>
       <c r="AS18" t="n">
-        <v>225</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19">
@@ -3484,7 +3484,7 @@
         <v>35</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
         <v>1.13</v>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -4476,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         <v>4</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P30" t="n">
         <v>60</v>
@@ -4772,7 +4772,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="P31" t="n">
         <v>383</v>
@@ -4993,7 +4993,7 @@
         <v>35174</v>
       </c>
       <c r="AS32" t="n">
-        <v>11840</v>
+        <v>13840</v>
       </c>
     </row>
     <row r="33">
@@ -5124,7 +5124,7 @@
         <v>2599</v>
       </c>
       <c r="AS33" t="n">
-        <v>2155</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="34">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P34" t="n">
         <v>128</v>
@@ -5334,7 +5334,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P35" t="n">
         <v>79</v>
@@ -5420,7 +5420,7 @@
         <v>537</v>
       </c>
       <c r="AS35" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36">
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -5636,7 +5636,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -5787,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
         <v>5</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -6089,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1940</v>
       </c>
       <c r="P40" t="n">
         <v>7621</v>
@@ -6175,7 +6175,7 @@
         <v>70528</v>
       </c>
       <c r="AS40" t="n">
-        <v>17304</v>
+        <v>24332</v>
       </c>
     </row>
     <row r="41">
@@ -6240,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1560</v>
       </c>
       <c r="P41" t="n">
         <v>1300</v>
@@ -6326,7 +6326,7 @@
         <v>12494</v>
       </c>
       <c r="AS41" t="n">
-        <v>7940</v>
+        <v>9540</v>
       </c>
     </row>
     <row r="42">
@@ -6391,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="P42" t="n">
         <v>11894</v>
@@ -6477,7 +6477,7 @@
         <v>35687</v>
       </c>
       <c r="AS42" t="n">
-        <v>2650</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="43">
@@ -6542,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="P43" t="n">
         <v>524</v>
@@ -6628,7 +6628,7 @@
         <v>8030</v>
       </c>
       <c r="AS43" t="n">
-        <v>2140</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="44">
@@ -6759,7 +6759,7 @@
         <v>15532</v>
       </c>
       <c r="AS44" t="n">
-        <v>1700</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="45">
@@ -6824,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P45" t="n">
         <v>50</v>
@@ -6910,7 +6910,7 @@
         <v>4282</v>
       </c>
       <c r="AS45" t="n">
-        <v>620</v>
+        <v>750</v>
       </c>
     </row>
     <row r="46">
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P46" t="n">
         <v>102</v>
@@ -7061,7 +7061,7 @@
         <v>2359</v>
       </c>
       <c r="AS46" t="n">
-        <v>142</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47">
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>181.5</v>
       </c>
       <c r="P47" t="n">
         <v>103</v>
@@ -7212,7 +7212,7 @@
         <v>5810</v>
       </c>
       <c r="AS47" t="n">
-        <v>1118.85</v>
+        <v>1338.85</v>
       </c>
     </row>
     <row r="48">
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>52</v>
       </c>
       <c r="AS48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -7428,7 +7428,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="P49" t="n">
         <v>15</v>
@@ -7514,7 +7514,7 @@
         <v>4130</v>
       </c>
       <c r="AS49" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50">
@@ -7584,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>1051</v>
       </c>
       <c r="AS50" t="n">
-        <v>490</v>
+        <v>620</v>
       </c>
     </row>
     <row r="51">
@@ -8068,7 +8068,7 @@
         <v>44358</v>
       </c>
       <c r="AS53" t="n">
-        <v>10602</v>
+        <v>12652</v>
       </c>
     </row>
     <row r="54">
@@ -8451,7 +8451,7 @@
         <v>1</v>
       </c>
       <c r="AS56" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -8592,7 +8592,7 @@
         <v>100950</v>
       </c>
       <c r="AS57" t="n">
-        <v>302500</v>
+        <v>332500</v>
       </c>
     </row>
     <row r="58">
@@ -8723,7 +8723,7 @@
         <v>0.3</v>
       </c>
       <c r="AS58" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="59">
@@ -8929,7 +8929,7 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z60" t="n">
         <v>0.5</v>
@@ -9106,7 +9106,7 @@
         <v>0.15</v>
       </c>
       <c r="AS61" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="62">
@@ -9247,7 +9247,7 @@
         <v>59629</v>
       </c>
       <c r="AS62" t="n">
-        <v>362500</v>
+        <v>407500</v>
       </c>
     </row>
     <row r="63">
@@ -9650,7 +9650,7 @@
         <v>0.4</v>
       </c>
       <c r="AS65" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="66">
@@ -9791,7 +9791,7 @@
         <v>139458</v>
       </c>
       <c r="AS66" t="n">
-        <v>1189110</v>
+        <v>1339110</v>
       </c>
     </row>
     <row r="67">
@@ -9932,7 +9932,7 @@
         <v>5.5</v>
       </c>
       <c r="AS67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -9997,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P68" t="n">
         <v>34</v>
@@ -10148,7 +10148,7 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="P69" t="n">
         <v>8</v>
@@ -10238,7 +10238,7 @@
         <v>852.92</v>
       </c>
       <c r="AS69" t="n">
-        <v>1165.5</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="70">
@@ -10303,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2611</v>
       </c>
       <c r="P70" t="n">
         <v>344</v>
@@ -10393,7 +10393,7 @@
         <v>2506</v>
       </c>
       <c r="AS70" t="n">
-        <v>3398.5</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="71">
@@ -10548,7 +10548,7 @@
         <v>195344</v>
       </c>
       <c r="AS71" t="n">
-        <v>255214</v>
+        <v>288829</v>
       </c>
     </row>
     <row r="72">
@@ -10613,7 +10613,7 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="P72" t="n">
         <v>201</v>
@@ -10764,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P73" t="n">
         <v>426</v>
@@ -10854,7 +10854,7 @@
         <v>2598</v>
       </c>
       <c r="AS73" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="74">
@@ -10919,7 +10919,7 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -11005,7 +11005,7 @@
         <v>8</v>
       </c>
       <c r="AS74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -11070,7 +11070,7 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P75" t="n">
         <v>184</v>
@@ -11160,7 +11160,7 @@
         <v>1644</v>
       </c>
       <c r="AS75" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76">
@@ -11225,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>4112</v>
       </c>
       <c r="P76" t="n">
         <v>128609</v>
@@ -11315,7 +11315,7 @@
         <v>437087</v>
       </c>
       <c r="AS76" t="n">
-        <v>29690.5</v>
+        <v>33769</v>
       </c>
     </row>
     <row r="77">
@@ -11380,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>5153</v>
       </c>
       <c r="P77" t="n">
         <v>3372</v>
@@ -11470,7 +11470,7 @@
         <v>19820</v>
       </c>
       <c r="AS77" t="n">
-        <v>27130.25</v>
+        <v>30437</v>
       </c>
     </row>
     <row r="78">
@@ -11611,7 +11611,7 @@
         <v>3424</v>
       </c>
       <c r="AS78" t="n">
-        <v>2200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="79">
@@ -11750,7 +11750,7 @@
       <c r="AQ79" t="inlineStr"/>
       <c r="AR79" t="inlineStr"/>
       <c r="AS79" t="n">
-        <v>2432.5</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="80">
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" t="n">
         <v>0.25</v>
@@ -12328,7 +12328,7 @@
         <v>4527</v>
       </c>
       <c r="AS83" t="n">
-        <v>3675</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="84">
@@ -12598,7 +12598,7 @@
         <v>8433</v>
       </c>
       <c r="AS85" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="86">
@@ -12663,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
         <v>1</v>
@@ -12814,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
@@ -13023,18 +13023,14 @@
       <c r="AM88" t="n">
         <v>1</v>
       </c>
-      <c r="AN88" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN88" t="inlineStr"/>
       <c r="AO88" t="inlineStr"/>
       <c r="AP88" t="inlineStr"/>
       <c r="AQ88" t="inlineStr"/>
       <c r="AR88" t="n">
         <v>1</v>
       </c>
-      <c r="AS88" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13164,7 +13160,7 @@
         <v>3841</v>
       </c>
       <c r="AS89" t="n">
-        <v>3450</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="90">
@@ -13305,7 +13301,7 @@
         <v>217</v>
       </c>
       <c r="AS90" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
     </row>
     <row r="91">
@@ -13446,7 +13442,7 @@
         <v>58172</v>
       </c>
       <c r="AS91" t="n">
-        <v>7600</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="92">
@@ -13587,7 +13583,7 @@
         <v>99</v>
       </c>
       <c r="AS92" t="n">
-        <v>117</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93">
@@ -13652,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -13803,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P94" t="n">
         <v>16</v>
@@ -13893,7 +13889,7 @@
         <v>116</v>
       </c>
       <c r="AS94" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95">
@@ -13958,7 +13954,7 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P95" t="n">
         <v>367</v>
@@ -14048,7 +14044,7 @@
         <v>1277</v>
       </c>
       <c r="AS95" t="n">
-        <v>464</v>
+        <v>569</v>
       </c>
     </row>
     <row r="96">
@@ -14193,7 +14189,7 @@
         <v>561</v>
       </c>
       <c r="AS96" t="n">
-        <v>473.42</v>
+        <v>550.95</v>
       </c>
     </row>
     <row r="97">
@@ -14258,7 +14254,7 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>25039.92</v>
       </c>
       <c r="P97" t="n">
         <v>10051</v>
@@ -14348,7 +14344,7 @@
         <v>253007</v>
       </c>
       <c r="AS97" t="n">
-        <v>160691.06</v>
+        <v>180626.34</v>
       </c>
     </row>
     <row r="98">
@@ -14489,7 +14485,7 @@
         <v>8117</v>
       </c>
       <c r="AS98" t="n">
-        <v>500</v>
+        <v>615</v>
       </c>
     </row>
     <row r="99">
@@ -14554,7 +14550,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>143.42</v>
       </c>
       <c r="P99" t="n">
         <v>168</v>
@@ -14644,7 +14640,7 @@
         <v>733</v>
       </c>
       <c r="AS99" t="n">
-        <v>921.0599999999999</v>
+        <v>1035.06</v>
       </c>
     </row>
     <row r="100">
@@ -14709,7 +14705,7 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -14860,7 +14856,7 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
@@ -14946,7 +14942,7 @@
         <v>11</v>
       </c>
       <c r="AS101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -15011,7 +15007,7 @@
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
@@ -15097,7 +15093,7 @@
         <v>7</v>
       </c>
       <c r="AS102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -15303,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="P104" t="n">
         <v>0.21</v>
@@ -15389,7 +15385,7 @@
         <v>0.57</v>
       </c>
       <c r="AS104" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -15459,7 +15455,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U105" t="n">
         <v>1</v>
@@ -15595,7 +15591,7 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="P106" t="n">
         <v>4035</v>
@@ -15679,7 +15675,7 @@
       <c r="AQ106" t="inlineStr"/>
       <c r="AR106" t="inlineStr"/>
       <c r="AS106" t="n">
-        <v>38288</v>
+        <v>40202</v>
       </c>
     </row>
     <row r="107">
@@ -15820,7 +15816,7 @@
         <v>161126</v>
       </c>
       <c r="AS107" t="n">
-        <v>413922</v>
+        <v>498113</v>
       </c>
     </row>
   </sheetData>
